--- a/artfynd/A 43701-2023 artfynd.xlsx
+++ b/artfynd/A 43701-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43701-2023 artfynd.xlsx
+++ b/artfynd/A 43701-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6121,10 +6121,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>116521868</v>
+        <v>116521873</v>
       </c>
       <c r="B48" t="n">
-        <v>79642</v>
+        <v>90426</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6133,25 +6133,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>4660</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>346012</v>
+        <v>345975</v>
       </c>
       <c r="R48" t="n">
-        <v>6523624</v>
+        <v>6523646</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6223,10 +6223,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116521873</v>
+        <v>116521878</v>
       </c>
       <c r="B49" t="n">
-        <v>90426</v>
+        <v>5185</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6239,34 +6239,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4660</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>345975</v>
+        <v>345916</v>
       </c>
       <c r="R49" t="n">
-        <v>6523646</v>
+        <v>6523667</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6307,8 +6316,24 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6325,10 +6350,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>116521878</v>
+        <v>116521860</v>
       </c>
       <c r="B50" t="n">
-        <v>5185</v>
+        <v>100026</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6341,43 +6366,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>345916</v>
+        <v>346082</v>
       </c>
       <c r="R50" t="n">
-        <v>6523667</v>
+        <v>6523748</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6418,24 +6434,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6452,10 +6452,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116521860</v>
+        <v>116521828</v>
       </c>
       <c r="B51" t="n">
-        <v>100026</v>
+        <v>90407</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6468,21 +6468,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>346082</v>
+        <v>345998</v>
       </c>
       <c r="R51" t="n">
-        <v>6523748</v>
+        <v>6523545</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6538,6 +6538,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6554,10 +6569,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116521828</v>
+        <v>116521822</v>
       </c>
       <c r="B52" t="n">
-        <v>90407</v>
+        <v>74613</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6570,21 +6585,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6594,10 +6609,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>345998</v>
+        <v>346078</v>
       </c>
       <c r="R52" t="n">
-        <v>6523545</v>
+        <v>6523506</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6640,21 +6655,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6671,10 +6671,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116521822</v>
+        <v>116521833</v>
       </c>
       <c r="B53" t="n">
-        <v>74613</v>
+        <v>90426</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6687,21 +6687,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6426</v>
+        <v>4660</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>346078</v>
+        <v>345989</v>
       </c>
       <c r="R53" t="n">
-        <v>6523506</v>
+        <v>6523701</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6757,6 +6757,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6773,10 +6788,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116521833</v>
+        <v>116521857</v>
       </c>
       <c r="B54" t="n">
-        <v>90426</v>
+        <v>90453</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6789,21 +6804,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4660</v>
+        <v>1205</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6813,10 +6828,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>345989</v>
+        <v>346121</v>
       </c>
       <c r="R54" t="n">
-        <v>6523701</v>
+        <v>6523675</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6890,10 +6905,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116521857</v>
+        <v>116521870</v>
       </c>
       <c r="B55" t="n">
-        <v>90453</v>
+        <v>74613</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6906,21 +6921,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1205</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6930,10 +6945,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>346121</v>
+        <v>345994</v>
       </c>
       <c r="R55" t="n">
-        <v>6523675</v>
+        <v>6523636</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6976,21 +6991,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7007,7 +7007,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116521870</v>
+        <v>116521826</v>
       </c>
       <c r="B56" t="n">
         <v>74613</v>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>345994</v>
+        <v>346033</v>
       </c>
       <c r="R56" t="n">
-        <v>6523636</v>
+        <v>6523550</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116521826</v>
+        <v>116521820</v>
       </c>
       <c r="B57" t="n">
-        <v>74613</v>
+        <v>5185</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7125,34 +7125,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>346033</v>
+        <v>346062</v>
       </c>
       <c r="R57" t="n">
-        <v>6523550</v>
+        <v>6523489</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7195,6 +7200,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7211,10 +7231,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>116521820</v>
+        <v>116521865</v>
       </c>
       <c r="B58" t="n">
-        <v>5185</v>
+        <v>79642</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7223,43 +7243,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>346062</v>
+        <v>346022</v>
       </c>
       <c r="R58" t="n">
-        <v>6523489</v>
+        <v>6523633</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7302,21 +7317,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7333,7 +7333,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>116521865</v>
+        <v>116521861</v>
       </c>
       <c r="B59" t="n">
         <v>79642</v>
@@ -7373,10 +7373,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>346022</v>
+        <v>346031</v>
       </c>
       <c r="R59" t="n">
-        <v>6523633</v>
+        <v>6523685</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7435,10 +7435,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>116521861</v>
+        <v>116521869</v>
       </c>
       <c r="B60" t="n">
-        <v>79642</v>
+        <v>79602</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7447,25 +7447,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>346031</v>
+        <v>345998</v>
       </c>
       <c r="R60" t="n">
-        <v>6523685</v>
+        <v>6523636</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7521,6 +7521,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7537,10 +7552,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>116521869</v>
+        <v>116521852</v>
       </c>
       <c r="B61" t="n">
-        <v>79602</v>
+        <v>90453</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7553,21 +7568,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>1205</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7577,10 +7592,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>345998</v>
+        <v>346173</v>
       </c>
       <c r="R61" t="n">
-        <v>6523636</v>
+        <v>6523653</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7623,21 +7638,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7654,10 +7654,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>116521852</v>
+        <v>116521872</v>
       </c>
       <c r="B62" t="n">
-        <v>90453</v>
+        <v>94272</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7670,21 +7670,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1205</v>
+        <v>2667</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>346173</v>
+        <v>345978</v>
       </c>
       <c r="R62" t="n">
-        <v>6523653</v>
+        <v>6523642</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7740,6 +7740,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7756,10 +7771,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>116521872</v>
+        <v>116521831</v>
       </c>
       <c r="B63" t="n">
-        <v>94272</v>
+        <v>79642</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7768,25 +7783,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7796,10 +7811,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>345978</v>
+        <v>345985</v>
       </c>
       <c r="R63" t="n">
-        <v>6523642</v>
+        <v>6523689</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7845,17 +7860,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7873,7 +7888,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>116521831</v>
+        <v>116521864</v>
       </c>
       <c r="B64" t="n">
         <v>79642</v>
@@ -7913,10 +7928,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>345985</v>
+        <v>346026</v>
       </c>
       <c r="R64" t="n">
-        <v>6523689</v>
+        <v>6523635</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7959,21 +7974,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7990,10 +7990,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>116521864</v>
+        <v>116521827</v>
       </c>
       <c r="B65" t="n">
-        <v>79642</v>
+        <v>74613</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8002,25 +8002,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>346026</v>
+        <v>346008</v>
       </c>
       <c r="R65" t="n">
-        <v>6523635</v>
+        <v>6523530</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8092,10 +8092,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>116521827</v>
+        <v>116521832</v>
       </c>
       <c r="B66" t="n">
-        <v>74613</v>
+        <v>79642</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8104,25 +8104,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6426</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>346008</v>
+        <v>345989</v>
       </c>
       <c r="R66" t="n">
-        <v>6523530</v>
+        <v>6523701</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8194,10 +8194,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>116521832</v>
+        <v>116521874</v>
       </c>
       <c r="B67" t="n">
-        <v>79642</v>
+        <v>100026</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8206,25 +8206,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8234,10 +8234,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>345989</v>
+        <v>345970</v>
       </c>
       <c r="R67" t="n">
-        <v>6523701</v>
+        <v>6523665</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8296,7 +8296,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>116521874</v>
+        <v>116521877</v>
       </c>
       <c r="B68" t="n">
         <v>100026</v>
@@ -8336,10 +8336,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>345970</v>
+        <v>345958</v>
       </c>
       <c r="R68" t="n">
-        <v>6523665</v>
+        <v>6523686</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>116521877</v>
+        <v>116521862</v>
       </c>
       <c r="B69" t="n">
-        <v>100026</v>
+        <v>79642</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8410,25 +8410,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8438,10 +8438,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>345958</v>
+        <v>346020</v>
       </c>
       <c r="R69" t="n">
-        <v>6523686</v>
+        <v>6523671</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8484,6 +8484,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8500,10 +8515,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>116521862</v>
+        <v>116521867</v>
       </c>
       <c r="B70" t="n">
-        <v>79642</v>
+        <v>100026</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8512,25 +8527,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8540,10 +8555,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>346020</v>
+        <v>346017</v>
       </c>
       <c r="R70" t="n">
-        <v>6523671</v>
+        <v>6523623</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8586,21 +8601,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8617,10 +8617,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>116521867</v>
+        <v>116521876</v>
       </c>
       <c r="B71" t="n">
-        <v>100026</v>
+        <v>90850</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8633,21 +8633,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rigidoporus corticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8657,10 +8657,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>346017</v>
+        <v>345973</v>
       </c>
       <c r="R71" t="n">
-        <v>6523623</v>
+        <v>6523677</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8701,8 +8701,24 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8719,10 +8735,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>116521876</v>
+        <v>116521836</v>
       </c>
       <c r="B72" t="n">
-        <v>90850</v>
+        <v>74613</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8735,21 +8751,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5321</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8759,10 +8775,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>345973</v>
+        <v>345974</v>
       </c>
       <c r="R72" t="n">
-        <v>6523677</v>
+        <v>6523874</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8803,24 +8819,8 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8837,10 +8837,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>116521836</v>
+        <v>116521881</v>
       </c>
       <c r="B73" t="n">
-        <v>74613</v>
+        <v>79602</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8853,34 +8853,41 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>345974</v>
+        <v>345903</v>
       </c>
       <c r="R73" t="n">
-        <v>6523874</v>
+        <v>6523627</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8921,8 +8928,24 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8939,10 +8962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>116521881</v>
+        <v>116521858</v>
       </c>
       <c r="B74" t="n">
-        <v>79602</v>
+        <v>74613</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8955,41 +8978,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229497</v>
+        <v>6426</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Sågeviken, Dls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>345903</v>
+        <v>346134</v>
       </c>
       <c r="R74" t="n">
-        <v>6523627</v>
+        <v>6523744</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9030,23 +9046,22 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9064,10 +9079,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>116521858</v>
+        <v>116884817</v>
       </c>
       <c r="B75" t="n">
-        <v>74613</v>
+        <v>94303</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9080,21 +9095,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9104,10 +9119,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>346134</v>
+        <v>346112</v>
       </c>
       <c r="R75" t="n">
-        <v>6523744</v>
+        <v>6523762</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9178,123 +9193,6 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>116884817</v>
-      </c>
-      <c r="B76" t="n">
-        <v>94303</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>2818</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Herzogiella seligeri</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Sågeviken, Dls</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>346112</v>
-      </c>
-      <c r="R76" t="n">
-        <v>6523762</v>
-      </c>
-      <c r="S76" t="n">
-        <v>5</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Mellerud</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Dalskog</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
